--- a/data/trans_orig/P05A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>460788</t>
+          <t>461714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>524024</t>
+          <t>525268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>615321</t>
+          <t>617935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>691628</t>
+          <t>693143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1103271</t>
+          <t>1103803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1198455</t>
+          <t>1202372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321184</t>
+          <t>321005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383314</t>
+          <t>383768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457780</t>
+          <t>457498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>528891</t>
+          <t>530512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>796969</t>
+          <t>792100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>888403</t>
+          <t>886060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106216</t>
+          <t>108288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149933</t>
+          <t>153252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160731</t>
+          <t>161872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>212555</t>
+          <t>214013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>283048</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>351399</t>
+          <t>347368</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1031757</t>
+          <t>1033788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121856</t>
+          <t>1120919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>920141</t>
+          <t>913192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1006314</t>
+          <t>1003569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1970677</t>
+          <t>1972809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2097919</t>
+          <t>2099592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>610388</t>
+          <t>615291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>696096</t>
+          <t>698298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>517187</t>
+          <t>518156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>599046</t>
+          <t>597888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1146506</t>
+          <t>1150589</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1269322</t>
+          <t>1272291</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>198659</t>
+          <t>201243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255302</t>
+          <t>256778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203327</t>
+          <t>200810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261439</t>
+          <t>259003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>419066</t>
+          <t>417947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501271</t>
+          <t>497837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>199931</t>
+          <t>200324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246937</t>
+          <t>248194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>197459</t>
+          <t>199400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417219</t>
+          <t>415519</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>481126</t>
+          <t>479472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155709</t>
+          <t>157979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203789</t>
+          <t>204374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148215</t>
+          <t>147375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193093</t>
+          <t>191474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318566</t>
+          <t>318346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383580</t>
+          <t>381666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59841</t>
+          <t>60933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95143</t>
+          <t>96393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>52713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84416</t>
+          <t>84262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119654</t>
+          <t>120732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166262</t>
+          <t>165840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1740491</t>
+          <t>1726469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1852314</t>
+          <t>1851484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1775374</t>
+          <t>1778013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1901074</t>
+          <t>1898829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3536139</t>
+          <t>3550623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3719875</t>
+          <t>3714559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1133924</t>
+          <t>1131354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1243075</t>
+          <t>1243600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1161161</t>
+          <t>1154543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1276498</t>
+          <t>1274116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2320015</t>
+          <t>2321819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2490490</t>
+          <t>2486089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>392209</t>
+          <t>390009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468434</t>
+          <t>471460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>442679</t>
+          <t>443465</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>527803</t>
+          <t>528580</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>854692</t>
+          <t>856424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>972765</t>
+          <t>971399</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>468033</t>
+          <t>464956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>520575</t>
+          <t>516613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>621912</t>
+          <t>615003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>682198</t>
+          <t>680156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1102938</t>
+          <t>1101813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1183149</t>
+          <t>1182305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161887</t>
+          <t>165588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209531</t>
+          <t>210847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203391</t>
+          <t>205105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258166</t>
+          <t>261349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>381791</t>
+          <t>382835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>453497</t>
+          <t>454687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56018</t>
+          <t>55662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84736</t>
+          <t>83286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>126679</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>151728</t>
+          <t>150571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205595</t>
+          <t>202749</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1318879</t>
+          <t>1317313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1405232</t>
+          <t>1403786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1268273</t>
+          <t>1272219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1351155</t>
+          <t>1355198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2610085</t>
+          <t>2613348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2737096</t>
+          <t>2734226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>465070</t>
+          <t>469189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>544129</t>
+          <t>550389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>409457</t>
+          <t>408986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>485005</t>
+          <t>484430</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>897947</t>
+          <t>896276</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1010899</t>
+          <t>1000433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174387</t>
+          <t>172739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229460</t>
+          <t>228495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>196856</t>
+          <t>196505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256363</t>
+          <t>252506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384910</t>
+          <t>383862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>465790</t>
+          <t>466521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321494</t>
+          <t>321500</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368122</t>
+          <t>368719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>313344</t>
+          <t>312772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359467</t>
+          <t>359307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>647569</t>
+          <t>650243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>712501</t>
+          <t>713136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116968</t>
+          <t>118061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160101</t>
+          <t>159799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110562</t>
+          <t>109189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148809</t>
+          <t>146961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236420</t>
+          <t>239698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298074</t>
+          <t>296091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>78208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66216</t>
+          <t>65854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101051</t>
+          <t>100752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>121197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>169192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2143883</t>
+          <t>2141478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2255084</t>
+          <t>2256401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2241725</t>
+          <t>2241947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2359763</t>
+          <t>2349530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4419275</t>
+          <t>4421954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4579579</t>
+          <t>4576824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>777235</t>
+          <t>781971</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>885053</t>
+          <t>883949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>750669</t>
+          <t>755984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>851769</t>
+          <t>855089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1563708</t>
+          <t>1564146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1707192</t>
+          <t>1707818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297718</t>
+          <t>298334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>369379</t>
+          <t>370633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>373794</t>
+          <t>376845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>455127</t>
+          <t>452914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>692930</t>
+          <t>694658</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>797520</t>
+          <t>796569</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373165</t>
+          <t>371871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>408595</t>
+          <t>408657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>555921</t>
+          <t>556647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>591709</t>
+          <t>591647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>940295</t>
+          <t>939390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>990063</t>
+          <t>989386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92567</t>
+          <t>92402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101159</t>
+          <t>102468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131388</t>
+          <t>133005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215224</t>
+          <t>214865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59804</t>
+          <t>58605</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77861</t>
+          <t>76397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91606</t>
+          <t>94812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126470</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1699180</t>
+          <t>1697382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1928763</t>
+          <t>1937722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1674120</t>
+          <t>1675473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1875284</t>
+          <t>1863802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3407096</t>
+          <t>3402103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3709509</t>
+          <t>3702787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>236123</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>401923</t>
+          <t>403847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>222491</t>
+          <t>227117</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353246</t>
+          <t>351454</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>529074</t>
+          <t>525781</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>725969</t>
+          <t>730081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205635</t>
+          <t>206741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137187</t>
+          <t>140607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219863</t>
+          <t>223147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279949</t>
+          <t>287409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>407248</t>
+          <t>414203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415799</t>
+          <t>417876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>466584</t>
+          <t>466329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>416008</t>
+          <t>414678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>457327</t>
+          <t>459757</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>845414</t>
+          <t>845199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>915222</t>
+          <t>911989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107192</t>
+          <t>107291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149631</t>
+          <t>147950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114765</t>
+          <t>113467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>149500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230656</t>
+          <t>229515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285656</t>
+          <t>287319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>61176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97295</t>
+          <t>96862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75526</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>109466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145856</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193311</t>
+          <t>194946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2523423</t>
+          <t>2524513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2794608</t>
+          <t>2806160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2678998</t>
+          <t>2681783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2917332</t>
+          <t>2915803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5232209</t>
+          <t>5240006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5591252</t>
+          <t>5613250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>433176</t>
+          <t>409886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609884</t>
+          <t>606007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459677</t>
+          <t>452616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>608516</t>
+          <t>605194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>951247</t>
+          <t>952715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1187250</t>
+          <t>1188646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231656</t>
+          <t>225770</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>334720</t>
+          <t>338192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>283974</t>
+          <t>284622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>384611</t>
+          <t>381997</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>543149</t>
+          <t>549836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>701214</t>
+          <t>693431</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>461714</t>
+          <t>460055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>525268</t>
+          <t>526036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>617935</t>
+          <t>616917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>693143</t>
+          <t>694413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1103803</t>
+          <t>1102399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1202372</t>
+          <t>1197899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321005</t>
+          <t>321661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383768</t>
+          <t>385504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457498</t>
+          <t>455621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>530512</t>
+          <t>528714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>792100</t>
+          <t>794956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>886060</t>
+          <t>888120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153252</t>
+          <t>148643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>162151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214013</t>
+          <t>211752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283048</t>
+          <t>281121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>347368</t>
+          <t>346896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1033788</t>
+          <t>1028348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120919</t>
+          <t>1117998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>913192</t>
+          <t>917368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1003569</t>
+          <t>1000581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972809</t>
+          <t>1976766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2099592</t>
+          <t>2100510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>615291</t>
+          <t>617849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>698298</t>
+          <t>698714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>518156</t>
+          <t>518066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>597888</t>
+          <t>598550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1150589</t>
+          <t>1148014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1272291</t>
+          <t>1269340</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201243</t>
+          <t>200185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256778</t>
+          <t>258277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200810</t>
+          <t>199119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259003</t>
+          <t>260462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>417947</t>
+          <t>418588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>497837</t>
+          <t>500280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>200324</t>
+          <t>201747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248194</t>
+          <t>249905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199400</t>
+          <t>199739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244338</t>
+          <t>245112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>415519</t>
+          <t>413811</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>479472</t>
+          <t>480876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157979</t>
+          <t>158732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204374</t>
+          <t>204512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147375</t>
+          <t>148051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191474</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318346</t>
+          <t>317523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381666</t>
+          <t>380551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96393</t>
+          <t>91541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>51242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84262</t>
+          <t>84411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120732</t>
+          <t>119287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165840</t>
+          <t>166940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1726469</t>
+          <t>1734596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1851484</t>
+          <t>1852011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1778013</t>
+          <t>1780645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1898829</t>
+          <t>1901648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3550623</t>
+          <t>3542345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3714559</t>
+          <t>3723214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1131354</t>
+          <t>1133972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1243600</t>
+          <t>1246945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1154543</t>
+          <t>1155474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1274116</t>
+          <t>1266712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2321819</t>
+          <t>2313454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2486089</t>
+          <t>2478360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>390009</t>
+          <t>391813</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471460</t>
+          <t>472399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>443465</t>
+          <t>442458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>528580</t>
+          <t>525219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>856424</t>
+          <t>860637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>971399</t>
+          <t>974041</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464956</t>
+          <t>467947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>516613</t>
+          <t>517907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>615003</t>
+          <t>619036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>680156</t>
+          <t>678231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1101813</t>
+          <t>1098352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1182305</t>
+          <t>1179191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165588</t>
+          <t>161874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210847</t>
+          <t>208907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205105</t>
+          <t>205533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261349</t>
+          <t>261040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382835</t>
+          <t>384112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>454687</t>
+          <t>456457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87589</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83286</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>127530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150571</t>
+          <t>152210</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202749</t>
+          <t>205972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1317313</t>
+          <t>1315434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1403786</t>
+          <t>1402296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1272219</t>
+          <t>1265502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1355198</t>
+          <t>1353121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2613348</t>
+          <t>2606933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2734226</t>
+          <t>2733051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>469189</t>
+          <t>467174</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>550389</t>
+          <t>549347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>408986</t>
+          <t>410614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>484430</t>
+          <t>482629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>896276</t>
+          <t>898447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1000433</t>
+          <t>1002160</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172739</t>
+          <t>173636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228495</t>
+          <t>230298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>196505</t>
+          <t>197872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252506</t>
+          <t>257287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>383862</t>
+          <t>381689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466521</t>
+          <t>461090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321500</t>
+          <t>320935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368719</t>
+          <t>367714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312772</t>
+          <t>312527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359307</t>
+          <t>359076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>650243</t>
+          <t>646430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>713136</t>
+          <t>712285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118061</t>
+          <t>117759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159799</t>
+          <t>159829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109189</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146961</t>
+          <t>151334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239698</t>
+          <t>238274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296091</t>
+          <t>295214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78208</t>
+          <t>75873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>65566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100752</t>
+          <t>99742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121197</t>
+          <t>121703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169192</t>
+          <t>166582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2141478</t>
+          <t>2144625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2256401</t>
+          <t>2253535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,47 +4170,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2297759</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2238348</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2355202</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>63,7%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2172</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2297759</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2241947</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2349530</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4421954</t>
+          <t>4413093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4576824</t>
+          <t>4578978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>781971</t>
+          <t>780207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>883949</t>
+          <t>878130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>755984</t>
+          <t>757744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>855089</t>
+          <t>855968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1564146</t>
+          <t>1562944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1707818</t>
+          <t>1704218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>298334</t>
+          <t>297184</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>370633</t>
+          <t>367533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>376845</t>
+          <t>372868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>452914</t>
+          <t>455864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>694658</t>
+          <t>693031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>796569</t>
+          <t>794579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>391480</t>
+          <t>440562</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371871</t>
+          <t>418824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>408657</t>
+          <t>458248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4872,32 +4872,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>574180</t>
+          <t>626041</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>556647</t>
+          <t>606148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>591647</t>
+          <t>644986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>965662</t>
+          <t>1066603</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>939390</t>
+          <t>1040868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>989386</t>
+          <t>1093559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75711</t>
+          <t>86951</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>104890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4985,32 +4985,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>126184</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>109878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133005</t>
+          <t>142990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>192687</t>
+          <t>213134</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174510</t>
+          <t>191334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214865</t>
+          <t>236150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -5063,32 +5063,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58605</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5098,32 +5098,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>69221</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>58440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>82571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>110009</t>
+          <t>118599</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94812</t>
+          <t>100405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129667</t>
+          <t>137755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513380</t>
+          <t>576891</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513380</t>
+          <t>576891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513380</t>
+          <t>576891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754977</t>
+          <t>821445</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754977</t>
+          <t>821445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754977</t>
+          <t>821445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1268358</t>
+          <t>1398336</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1268358</t>
+          <t>1398336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1268358</t>
+          <t>1398336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5293,32 +5293,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1776399</t>
+          <t>1658610</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1697382</t>
+          <t>1604131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1937722</t>
+          <t>1700401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1748215</t>
+          <t>1605263</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1675473</t>
+          <t>1568307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1863802</t>
+          <t>1649300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3524614</t>
+          <t>3263873</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3402103</t>
+          <t>3205933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3702787</t>
+          <t>3326957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>344586</t>
+          <t>380975</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236123</t>
+          <t>348118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>403847</t>
+          <t>426942</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>303151</t>
+          <t>348837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227117</t>
+          <t>314414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>351454</t>
+          <t>380848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>647736</t>
+          <t>729812</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>525781</t>
+          <t>672459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>730081</t>
+          <t>776839</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5519,32 +5519,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>169342</t>
+          <t>190980</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>160653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206741</t>
+          <t>221074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>186135</t>
+          <t>214182</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140607</t>
+          <t>189895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223147</t>
+          <t>246013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>355477</t>
+          <t>405162</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287409</t>
+          <t>368140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>414203</t>
+          <t>443621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -5632,17 +5632,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237500</t>
+          <t>2168281</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237500</t>
+          <t>2168281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237500</t>
+          <t>2168281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4527827</t>
+          <t>4398847</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4527827</t>
+          <t>4398847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4527827</t>
+          <t>4398847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>442411</t>
+          <t>484215</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>417876</t>
+          <t>456818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>466329</t>
+          <t>511440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>437708</t>
+          <t>486357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>414678</t>
+          <t>463400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459757</t>
+          <t>508950</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>880119</t>
+          <t>970572</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>845199</t>
+          <t>933182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>911989</t>
+          <t>1003100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126395</t>
+          <t>142305</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107291</t>
+          <t>119841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147950</t>
+          <t>168469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130256</t>
+          <t>145251</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>128030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149500</t>
+          <t>165737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>256651</t>
+          <t>287556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229515</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>287319</t>
+          <t>320909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5975,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77817</t>
+          <t>85067</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>69381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96862</t>
+          <t>106251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91157</t>
+          <t>101838</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75062</t>
+          <t>85765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>121529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6045,32 +6045,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>168974</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146931</t>
+          <t>163957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194946</t>
+          <t>215862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6088,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2610291</t>
+          <t>2583387</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2524513</t>
+          <t>2527080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2806160</t>
+          <t>2643472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6240,32 +6240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2760103</t>
+          <t>2717661</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2681783</t>
+          <t>2668934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2915803</t>
+          <t>2769192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5370393</t>
+          <t>5301048</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5240006</t>
+          <t>5216070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5613250</t>
+          <t>5373930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -6318,32 +6318,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546692</t>
+          <t>610231</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409886</t>
+          <t>559466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606007</t>
+          <t>659715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6353,32 +6353,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>550383</t>
+          <t>620271</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452616</t>
+          <t>578188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>605194</t>
+          <t>661338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1097074</t>
+          <t>1230502</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>952715</t>
+          <t>1168573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188646</t>
+          <t>1296546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6431,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>293348</t>
+          <t>325426</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>225770</t>
+          <t>289736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>338192</t>
+          <t>360958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>341112</t>
+          <t>385241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284622</t>
+          <t>351073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381997</t>
+          <t>424482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>634460</t>
+          <t>710667</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>549836</t>
+          <t>662638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>693431</t>
+          <t>761830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -6544,17 +6544,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450331</t>
+          <t>3519044</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450331</t>
+          <t>3519044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450331</t>
+          <t>3519044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3651598</t>
+          <t>3723172</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3651598</t>
+          <t>3723172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3651598</t>
+          <t>3723172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7101928</t>
+          <t>7242216</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7101928</t>
+          <t>7242216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7101928</t>
+          <t>7242216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
